--- a/riverhouse/River House 2026_2027 Room Map Out .xlsx
+++ b/riverhouse/River House 2026_2027 Room Map Out .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brian\Documents\GitHub\cmpmarketinghub\riverhouse\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC4B1204-0D3D-4F2E-8619-6690AF719F12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF1F0C0E-9EE1-4960-A79D-52BF25D8FAFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2268,7 +2268,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:I271"/>
-  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.59765625" style="6"/>
   </cols>
